--- a/fy26_dashboard_data.xlsx
+++ b/fy26_dashboard_data.xlsx
@@ -502,28 +502,28 @@
         <v>100706.205162901</v>
       </c>
       <c r="D2" t="n">
-        <v>108119.3385714286</v>
+        <v>124975.3671428571</v>
       </c>
       <c r="E2" t="n">
-        <v>1.073611485970862</v>
+        <v>1.240989737828952</v>
       </c>
       <c r="F2" t="n">
-        <v>-7413.133408527618</v>
+        <v>-24269.16197995619</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.07361148597086184</v>
+        <v>-0.2409897378289524</v>
       </c>
       <c r="H2" t="n">
-        <v>1100355.123383383</v>
+        <v>1083499.094811954</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9105323761690949</v>
+        <v>0.896584188514254</v>
       </c>
       <c r="J2" t="n">
-        <v>29814.08571428571</v>
+        <v>32131.58571428571</v>
       </c>
       <c r="K2" t="n">
-        <v>2.626451590954611</v>
+        <v>2.889486446580601</v>
       </c>
     </row>
     <row r="3">
@@ -538,31 +538,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100032.2839439439</v>
+        <v>98499.91771017766</v>
       </c>
       <c r="D3" t="n">
-        <v>78099.57857142857</v>
+        <v>82257.50714285714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.780743730845874</v>
+        <v>0.8351022930281875</v>
       </c>
       <c r="F3" t="n">
-        <v>21932.70537251532</v>
+        <v>16242.41056732052</v>
       </c>
       <c r="G3" t="n">
-        <v>0.219256269154126</v>
+        <v>0.1648977069718125</v>
       </c>
       <c r="H3" t="n">
-        <v>1022255.544811954</v>
+        <v>1001241.587669097</v>
       </c>
       <c r="I3" t="n">
-        <v>0.845905790312166</v>
+        <v>0.8285169601759749</v>
       </c>
       <c r="J3" t="n">
-        <v>46804.82857142857</v>
+        <v>52622.32857142857</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6686222544804595</v>
+        <v>0.5631673735456675</v>
       </c>
     </row>
     <row r="4">
@@ -577,31 +577,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>102225.5544811954</v>
+        <v>100124.1587669097</v>
       </c>
       <c r="D4" t="n">
-        <v>104299.4742857143</v>
+        <v>108242.9742857143</v>
       </c>
       <c r="E4" t="n">
-        <v>1.020287684572064</v>
+        <v>1.081087477975273</v>
       </c>
       <c r="F4" t="n">
-        <v>-2073.919804518853</v>
+        <v>-8118.815518804578</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.02028768457206416</v>
+        <v>-0.08108747797527351</v>
       </c>
       <c r="H4" t="n">
-        <v>917956.0705262399</v>
+        <v>892998.6133833828</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7595990642957957</v>
+        <v>0.7389470290823363</v>
       </c>
       <c r="J4" t="n">
-        <v>55460.50714285714</v>
+        <v>57913.00714285715</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8806080156652013</v>
+        <v>0.8690615394691125</v>
       </c>
     </row>
     <row r="5">
@@ -616,31 +616,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>101995.11894736</v>
+        <v>99222.0681537092</v>
       </c>
       <c r="D5" t="n">
-        <v>65806.29785714285</v>
+        <v>66185.29785714285</v>
       </c>
       <c r="E5" t="n">
-        <v>0.645190657516716</v>
+        <v>0.6670421115856237</v>
       </c>
       <c r="F5" t="n">
-        <v>36188.82109021714</v>
+        <v>33036.77029656635</v>
       </c>
       <c r="G5" t="n">
-        <v>0.354809342483284</v>
+        <v>0.3329578884143763</v>
       </c>
       <c r="H5" t="n">
-        <v>852149.7726690971</v>
+        <v>826813.3155262399</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7051450398800083</v>
+        <v>0.684179386123558</v>
       </c>
       <c r="J5" t="n">
-        <v>85337.96428571429</v>
+        <v>91419.39285714286</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2288742951868266</v>
+        <v>-0.2760256244474543</v>
       </c>
     </row>
     <row r="6">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>106518.7215836371</v>
+        <v>103351.66444078</v>
       </c>
       <c r="D6" t="n">
-        <v>53041.26428571429</v>
+        <v>76085.24285714286</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4979525054106753</v>
+        <v>0.7361782054389587</v>
       </c>
       <c r="F6" t="n">
-        <v>53477.45729792285</v>
+        <v>27266.42158363713</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5020474945893247</v>
+        <v>0.2638217945610412</v>
       </c>
       <c r="H6" t="n">
-        <v>799108.5083833828</v>
+        <v>750728.0726690971</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6612539474692383</v>
+        <v>0.6212196420392119</v>
       </c>
       <c r="J6" t="n">
-        <v>105790.9642857143</v>
+        <v>112683.5357142857</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4986219792603136</v>
+        <v>-0.3247882898344573</v>
       </c>
     </row>
     <row r="7">
@@ -853,28 +853,28 @@
         <v>98808.69569837145</v>
       </c>
       <c r="D11" t="n">
-        <v>17881.58571428572</v>
+        <v>20873.87857142857</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1809717817637425</v>
+        <v>0.2112554813510468</v>
       </c>
       <c r="F11" t="n">
-        <v>80927.10998408574</v>
+        <v>77934.81712694289</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8190282182362576</v>
+        <v>0.7887445186489532</v>
       </c>
       <c r="H11" t="n">
-        <v>772587.9798726859</v>
+        <v>769595.687015543</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8662614814668295</v>
+        <v>0.8629063839103825</v>
       </c>
       <c r="J11" t="n">
         <v>19929.815</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1027721173384842</v>
+        <v>0.04736940967232114</v>
       </c>
     </row>
     <row r="12">
@@ -1048,28 +1048,28 @@
         <v>90260.810030765</v>
       </c>
       <c r="D16" t="n">
-        <v>20707</v>
+        <v>25428.42857142857</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2294129644188005</v>
+        <v>0.2817216969663955</v>
       </c>
       <c r="F16" t="n">
-        <v>69553.810030765</v>
+        <v>64832.38145933643</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7705870355811996</v>
+        <v>0.7182783030336045</v>
       </c>
       <c r="H16" t="n">
-        <v>701379.48024612</v>
+        <v>696658.0516746915</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8483943625065021</v>
+        <v>0.8426832838453878</v>
       </c>
       <c r="J16" t="n">
         <v>26976.62142857143</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2324094381193028</v>
+        <v>-0.05739016878900702</v>
       </c>
     </row>
     <row r="17">
@@ -1243,28 +1243,28 @@
         <v>103460.7172109365</v>
       </c>
       <c r="D21" t="n">
-        <v>4874.25</v>
+        <v>7028.978571428572</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04711208400056172</v>
+        <v>0.06793862212551494</v>
       </c>
       <c r="F21" t="n">
-        <v>98586.46721093646</v>
+        <v>96431.73863950789</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9528879159994382</v>
+        <v>0.9320613778744851</v>
       </c>
       <c r="H21" t="n">
-        <v>822811.4876874917</v>
+        <v>820656.7591160631</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9451482480430509</v>
+        <v>0.942673151420351</v>
       </c>
       <c r="J21" t="n">
         <v>29377.92857142857</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8340846262135568</v>
+        <v>-0.7607394764290977</v>
       </c>
     </row>
   </sheetData>
@@ -1348,28 +1348,28 @@
         <v>1208474.461954811</v>
       </c>
       <c r="C2" t="n">
-        <v>511477.8841190374</v>
+        <v>501904.0142344775</v>
       </c>
       <c r="D2" t="n">
-        <v>409365.9535714286</v>
+        <v>457746.3892857143</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3387460525307618</v>
+        <v>0.3787803579607881</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8003590502774426</v>
+        <v>0.912019781280064</v>
       </c>
       <c r="G2" t="n">
-        <v>799108.5083833828</v>
+        <v>750728.0726690971</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6612539474692383</v>
+        <v>0.6212196420392119</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8035572128632383</v>
+        <v>0.9120799651713993</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2665698567856574</v>
+        <v>0.320029377657009</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1390,25 +1390,25 @@
         <v>427084.7122117203</v>
       </c>
       <c r="D3" t="n">
-        <v>119276.655</v>
+        <v>122268.9478571429</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1337385185331705</v>
+        <v>0.1370936160896175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2792810222176029</v>
+        <v>0.2862873438479109</v>
       </c>
       <c r="G3" t="n">
-        <v>772587.9798726859</v>
+        <v>769595.687015543</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8662614814668295</v>
+        <v>0.8629063839103825</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2830593223504769</v>
+        <v>0.2891160622679377</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3420639563424138</v>
+        <v>0.3757323082122099</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         <v>392619.1674257526</v>
       </c>
       <c r="D4" t="n">
-        <v>125334.5</v>
+        <v>130055.9285714286</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1516056374934978</v>
+        <v>0.1573167161546122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3192266460696975</v>
+        <v>0.3312521123819641</v>
       </c>
       <c r="G4" t="n">
-        <v>701379.48024612</v>
+        <v>696658.0516746915</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8483943625065021</v>
+        <v>0.8426832838453878</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3234291975678416</v>
+        <v>0.3338909440773606</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.006731653171787003</v>
+        <v>0.03068538325322253</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1468,25 +1468,25 @@
         <v>430597.0695008999</v>
       </c>
       <c r="D5" t="n">
-        <v>47751.92857142857</v>
+        <v>49906.65714285715</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05485175195694916</v>
+        <v>0.0573268485796491</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1108970124361907</v>
+        <v>0.1159010608239935</v>
       </c>
       <c r="G5" t="n">
-        <v>822811.4876874917</v>
+        <v>820656.7591160631</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9451482480430509</v>
+        <v>0.942673151420351</v>
       </c>
       <c r="I5" t="n">
-        <v>0.118354348884878</v>
+        <v>0.1225196565098687</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4967212165710476</v>
+        <v>-0.4740115751703644</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-28 14:26:51</t>
+          <t>2026-05-04 12:59:16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
